--- a/golf_streamlit/data/hullinfo.xlsx
+++ b/golf_streamlit/data/hullinfo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c624kh1\Documents\My Projects\min_git\golf_streamlit\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C3FEE9-F1EF-4190-A1A9-86EB3F91C3EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7EDAA14-C4E9-4DAA-8C3F-6A90E4D28B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="19">
   <si>
     <t>Bane</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>Miklagard</t>
+  </si>
+  <si>
+    <t>The Club at Olde Stone</t>
   </si>
 </sst>
 </file>
@@ -456,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I244"/>
+  <dimension ref="A1:I262"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.33203125" customWidth="1"/>
@@ -3080,7 +3083,7 @@
         <v>4</v>
       </c>
       <c r="C176">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D176">
         <v>5</v>
@@ -3094,7 +3097,7 @@
         <v>5</v>
       </c>
       <c r="C177">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D177">
         <v>9</v>
@@ -3108,7 +3111,7 @@
         <v>6</v>
       </c>
       <c r="C178">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D178">
         <v>15</v>
@@ -3136,7 +3139,7 @@
         <v>8</v>
       </c>
       <c r="C180">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D180">
         <v>3</v>
@@ -3178,7 +3181,7 @@
         <v>11</v>
       </c>
       <c r="C183">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D183">
         <v>2</v>
@@ -3206,7 +3209,7 @@
         <v>13</v>
       </c>
       <c r="C185">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D185">
         <v>12</v>
@@ -3234,7 +3237,7 @@
         <v>15</v>
       </c>
       <c r="C187">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D187">
         <v>16</v>
@@ -3262,7 +3265,7 @@
         <v>17</v>
       </c>
       <c r="C189">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D189">
         <v>14</v>
@@ -3276,7 +3279,7 @@
         <v>18</v>
       </c>
       <c r="C190">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D190">
         <v>18</v>
@@ -4036,6 +4039,258 @@
       </c>
       <c r="D244">
         <v>9</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>18</v>
+      </c>
+      <c r="B245">
+        <v>1</v>
+      </c>
+      <c r="C245">
+        <v>4</v>
+      </c>
+      <c r="D245">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>18</v>
+      </c>
+      <c r="B246">
+        <v>2</v>
+      </c>
+      <c r="C246">
+        <v>5</v>
+      </c>
+      <c r="D246">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>18</v>
+      </c>
+      <c r="B247">
+        <v>3</v>
+      </c>
+      <c r="C247">
+        <v>3</v>
+      </c>
+      <c r="D247">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>18</v>
+      </c>
+      <c r="B248">
+        <v>4</v>
+      </c>
+      <c r="C248">
+        <v>4</v>
+      </c>
+      <c r="D248">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>18</v>
+      </c>
+      <c r="B249">
+        <v>5</v>
+      </c>
+      <c r="C249">
+        <v>4</v>
+      </c>
+      <c r="D249">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>18</v>
+      </c>
+      <c r="B250">
+        <v>6</v>
+      </c>
+      <c r="C250">
+        <v>4</v>
+      </c>
+      <c r="D250">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>18</v>
+      </c>
+      <c r="B251">
+        <v>7</v>
+      </c>
+      <c r="C251">
+        <v>5</v>
+      </c>
+      <c r="D251">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>18</v>
+      </c>
+      <c r="B252">
+        <v>8</v>
+      </c>
+      <c r="C252">
+        <v>3</v>
+      </c>
+      <c r="D252">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>18</v>
+      </c>
+      <c r="B253">
+        <v>9</v>
+      </c>
+      <c r="C253">
+        <v>4</v>
+      </c>
+      <c r="D253">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>18</v>
+      </c>
+      <c r="B254">
+        <v>10</v>
+      </c>
+      <c r="C254">
+        <v>4</v>
+      </c>
+      <c r="D254">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>18</v>
+      </c>
+      <c r="B255">
+        <v>11</v>
+      </c>
+      <c r="C255">
+        <v>5</v>
+      </c>
+      <c r="D255">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>18</v>
+      </c>
+      <c r="B256">
+        <v>12</v>
+      </c>
+      <c r="C256">
+        <v>4</v>
+      </c>
+      <c r="D256">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>18</v>
+      </c>
+      <c r="B257">
+        <v>13</v>
+      </c>
+      <c r="C257">
+        <v>3</v>
+      </c>
+      <c r="D257">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>18</v>
+      </c>
+      <c r="B258">
+        <v>14</v>
+      </c>
+      <c r="C258">
+        <v>4</v>
+      </c>
+      <c r="D258">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>18</v>
+      </c>
+      <c r="B259">
+        <v>15</v>
+      </c>
+      <c r="C259">
+        <v>4</v>
+      </c>
+      <c r="D259">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>18</v>
+      </c>
+      <c r="B260">
+        <v>16</v>
+      </c>
+      <c r="C260">
+        <v>3</v>
+      </c>
+      <c r="D260">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>18</v>
+      </c>
+      <c r="B261">
+        <v>17</v>
+      </c>
+      <c r="C261">
+        <v>4</v>
+      </c>
+      <c r="D261">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>18</v>
+      </c>
+      <c r="B262">
+        <v>18</v>
+      </c>
+      <c r="C262">
+        <v>5</v>
+      </c>
+      <c r="D262">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/golf_streamlit/data/hullinfo.xlsx
+++ b/golf_streamlit/data/hullinfo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c624kh1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\c624kh1\Documents\My Projects\min_git\golf_streamlit\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26BB7184-574A-4B85-A4A9-413B76BB01D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7EDAA14-C4E9-4DAA-8C3F-6A90E4D28B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="19">
   <si>
     <t>Bane</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>Miklagard</t>
+  </si>
+  <si>
+    <t>The Club at Olde Stone</t>
   </si>
 </sst>
 </file>
@@ -456,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I244"/>
+  <dimension ref="A1:I262"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.33203125" customWidth="1"/>
@@ -4036,6 +4039,258 @@
       </c>
       <c r="D244">
         <v>9</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>18</v>
+      </c>
+      <c r="B245">
+        <v>1</v>
+      </c>
+      <c r="C245">
+        <v>4</v>
+      </c>
+      <c r="D245">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>18</v>
+      </c>
+      <c r="B246">
+        <v>2</v>
+      </c>
+      <c r="C246">
+        <v>5</v>
+      </c>
+      <c r="D246">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>18</v>
+      </c>
+      <c r="B247">
+        <v>3</v>
+      </c>
+      <c r="C247">
+        <v>3</v>
+      </c>
+      <c r="D247">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>18</v>
+      </c>
+      <c r="B248">
+        <v>4</v>
+      </c>
+      <c r="C248">
+        <v>4</v>
+      </c>
+      <c r="D248">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>18</v>
+      </c>
+      <c r="B249">
+        <v>5</v>
+      </c>
+      <c r="C249">
+        <v>4</v>
+      </c>
+      <c r="D249">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>18</v>
+      </c>
+      <c r="B250">
+        <v>6</v>
+      </c>
+      <c r="C250">
+        <v>4</v>
+      </c>
+      <c r="D250">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>18</v>
+      </c>
+      <c r="B251">
+        <v>7</v>
+      </c>
+      <c r="C251">
+        <v>5</v>
+      </c>
+      <c r="D251">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>18</v>
+      </c>
+      <c r="B252">
+        <v>8</v>
+      </c>
+      <c r="C252">
+        <v>3</v>
+      </c>
+      <c r="D252">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>18</v>
+      </c>
+      <c r="B253">
+        <v>9</v>
+      </c>
+      <c r="C253">
+        <v>4</v>
+      </c>
+      <c r="D253">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>18</v>
+      </c>
+      <c r="B254">
+        <v>10</v>
+      </c>
+      <c r="C254">
+        <v>4</v>
+      </c>
+      <c r="D254">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>18</v>
+      </c>
+      <c r="B255">
+        <v>11</v>
+      </c>
+      <c r="C255">
+        <v>5</v>
+      </c>
+      <c r="D255">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>18</v>
+      </c>
+      <c r="B256">
+        <v>12</v>
+      </c>
+      <c r="C256">
+        <v>4</v>
+      </c>
+      <c r="D256">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>18</v>
+      </c>
+      <c r="B257">
+        <v>13</v>
+      </c>
+      <c r="C257">
+        <v>3</v>
+      </c>
+      <c r="D257">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>18</v>
+      </c>
+      <c r="B258">
+        <v>14</v>
+      </c>
+      <c r="C258">
+        <v>4</v>
+      </c>
+      <c r="D258">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>18</v>
+      </c>
+      <c r="B259">
+        <v>15</v>
+      </c>
+      <c r="C259">
+        <v>4</v>
+      </c>
+      <c r="D259">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>18</v>
+      </c>
+      <c r="B260">
+        <v>16</v>
+      </c>
+      <c r="C260">
+        <v>3</v>
+      </c>
+      <c r="D260">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>18</v>
+      </c>
+      <c r="B261">
+        <v>17</v>
+      </c>
+      <c r="C261">
+        <v>4</v>
+      </c>
+      <c r="D261">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>18</v>
+      </c>
+      <c r="B262">
+        <v>18</v>
+      </c>
+      <c r="C262">
+        <v>5</v>
+      </c>
+      <c r="D262">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
